--- a/public/files/danh_sach_san_pham_mau.xlsx
+++ b/public/files/danh_sach_san_pham_mau.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\job-part-time\nextjs-antd-admin\public\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E06813-1F1D-472C-8922-8869FF943A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4792DBED-A917-4961-B255-2B6C27F3005F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>STT</t>
   </si>
@@ -44,9 +44,6 @@
   </si>
   <si>
     <t>Tồn kho hiện tại</t>
-  </si>
-  <si>
-    <t>Tồn kho tổng</t>
   </si>
   <si>
     <t>Trạng thái (0: Ngừng, 1: Hoạt động)</t>
@@ -457,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.75" bestFit="1" customWidth="1"/>
@@ -467,12 +464,11 @@
     <col min="5" max="5" width="9.75" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="8.875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -503,25 +499,22 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>13</v>
-      </c>
-      <c r="E2" t="s">
-        <v>14</v>
       </c>
       <c r="F2">
         <v>10000</v>
@@ -533,24 +526,21 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>225</v>
-      </c>
-      <c r="J2">
         <v>1</v>
       </c>
-      <c r="K2" t="s">
-        <v>15</v>
+      <c r="J2" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
         <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
       </c>
       <c r="F3">
         <v>30000</v>
@@ -561,14 +551,14 @@
       <c r="H3">
         <v>60</v>
       </c>
-      <c r="J3">
+      <c r="I3">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:K2" numberStoredAsText="1"/>
+    <ignoredError sqref="A2:H2 A1:G1 I1:J1 I2:J2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>